--- a/music-metadata-da.xlsx
+++ b/music-metadata-da.xlsx
@@ -19,8 +19,8 @@
     <sheet name="Sheet14" sheetId="15" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlcn.WorksheetConnection_MusicMetadataTHT.xlsxmusicmd" hidden="1">musicmd[]</definedName>
-    <definedName name="_xlcn.WorksheetConnection_Sheet1H2H1048576" hidden="1">Sheet1!$H$2:$H$1048576</definedName>
+    <definedName name="_xlcn.WorksheetConnection_MusicMetadataTHT.xlsxmusicmd1" hidden="1">musicmd[]</definedName>
+    <definedName name="_xlcn.WorksheetConnection_Sheet1H2H10485761" hidden="1">Sheet1!$H$2:$H$1048576</definedName>
     <definedName name="Slicer_Genre">#N/A</definedName>
     <definedName name="Slicer_Language">#N/A</definedName>
     <definedName name="Slicer_Performance_category">#N/A</definedName>
@@ -95,7 +95,7 @@
     <extLst>
       <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{DE250136-89BD-433C-8126-D09CA5730AF9}">
         <x15:connection id="musicmd" autoDelete="1">
-          <x15:rangePr sourceName="_xlcn.WorksheetConnection_MusicMetadataTHT.xlsxmusicmd"/>
+          <x15:rangePr sourceName="_xlcn.WorksheetConnection_MusicMetadataTHT.xlsxmusicmd1"/>
         </x15:connection>
       </ext>
     </extLst>
@@ -104,7 +104,7 @@
     <extLst>
       <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{DE250136-89BD-433C-8126-D09CA5730AF9}">
         <x15:connection id="Range" autoDelete="1">
-          <x15:rangePr sourceName="_xlcn.WorksheetConnection_Sheet1H2H1048576"/>
+          <x15:rangePr sourceName="_xlcn.WorksheetConnection_Sheet1H2H10485761"/>
         </x15:connection>
       </ext>
     </extLst>
